--- a/docs/ui/demo_input.xlsx
+++ b/docs/ui/demo_input.xlsx
@@ -17,6 +17,7 @@
     <sheet name="минимальные_остатки" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="ручные_назначения" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="ручные_запреты" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="правила_замещения" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'сотрудники'!$A$1:$L$2</definedName>
@@ -1214,6 +1215,36 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>должность</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>может быть замещена</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Лист3">

--- a/docs/ui/demo_input.xlsx
+++ b/docs/ui/demo_input.xlsx
@@ -2957,7 +2957,7 @@
         <v>40400</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>110000</v>
+        <v>200000</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>149648.9</v>

--- a/docs/ui/demo_input.xlsx
+++ b/docs/ui/demo_input.xlsx
@@ -1252,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1373,6 +1373,11 @@
       <c r="T1" s="2" t="inlineStr">
         <is>
           <t>конечная дата выплат надбавок</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>подразделение</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1826,7 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>500000</v>

--- a/docs/ui/demo_input.xlsx
+++ b/docs/ui/demo_input.xlsx
@@ -18,6 +18,7 @@
     <sheet name="ручные_назначения" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="ручные_запреты" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="правила_замещения" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="источники_справочника" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'сотрудники'!$A$1:$L$2</definedName>
@@ -1245,6 +1246,172 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>величина</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>документ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id документа</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>загружен</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>основание</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>действует с</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>записано</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>оклад</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>polozheniye_ob_oplate_truda_01-09-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>02.09.2026 09:08</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>09.09.2026 09:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>П2556</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MAX ЗП_Приказ № 2556 от 16.09.2025 О формировании заработной платы работников (3018611 v3)взамен пр.2706.DOC</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>02.09.2026 10:57</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Приказ № 2556 от 16.09.2025</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>01.12.2025</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>09.09.2026 11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>П4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Справка П4 2025.pdf</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>02.09.2026 09:08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>средняя зарплата по категории из справки / 1,086866 (без отпускных)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>09.09.2026 10:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>БЭП</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>БЭП 2025 550 ВП МО РФ.pdf</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>02.09.2026 08:53</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>09.09.2026 09:06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Лист3">
@@ -2962,7 +3129,7 @@
         <v>40400</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>200000</v>
+        <v>110000</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>149648.9</v>
